--- a/cities.xlsx
+++ b/cities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Документы\Проекты\2026 Проекты\Беговой\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CE6043-5F1F-418D-9AFA-519B8F982B47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D53B7B-D338-4D5A-8089-BC9061842762}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Владивосток</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Чита</t>
+  </si>
+  <si>
+    <t>Город</t>
+  </si>
+  <si>
+    <t>Расстояние</t>
   </si>
 </sst>
 </file>
@@ -485,329 +491,338 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2">
-        <v>0</v>
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>241</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>766</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2">
-        <v>938</v>
+        <v>766</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2">
-        <v>1983</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>2022</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>2178</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>3091</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2">
-        <v>3648</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2">
-        <v>4104</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2">
-        <v>4144</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2">
-        <v>4494</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2">
-        <v>4610</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2">
-        <v>4774</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2">
-        <v>4945</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2">
-        <v>5191</v>
+        <v>4945</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="B18" s="2">
-        <v>5375</v>
+        <v>5191</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2">
-        <v>5576</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2">
-        <v>5693</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="2">
-        <v>5805</v>
+        <v>5693</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2">
-        <v>5947</v>
+        <v>5805</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2">
-        <v>6102</v>
+        <v>5947</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2">
-        <v>6494</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2">
-        <v>6727</v>
+        <v>6494</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>7010</v>
+        <v>6727</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="2">
+        <v>7010</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B28" s="2">
         <v>7088</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="2">
-        <v>7299</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B29" s="2">
-        <v>7624</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>7903</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B31" s="2">
-        <v>8004</v>
+        <v>7903</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B32" s="2">
-        <v>8275</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" s="2">
-        <v>8482</v>
+        <v>8275</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2">
-        <v>8569</v>
+        <v>8482</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="2">
-        <v>8938</v>
+        <v>8569</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" s="2">
-        <v>9082</v>
+        <v>8938</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B37" s="2">
-        <v>9156</v>
+        <v>9082</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B38" s="2">
-        <v>9214</v>
+        <v>9156</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" s="2">
-        <v>9368</v>
+        <v>9214</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="2">
+        <v>9368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B41" s="2">
         <v>9438</v>
       </c>
     </row>
